--- a/ExcelFiles/Map.xlsx
+++ b/ExcelFiles/Map.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hdong\OneDrive\바탕 화면\ExampleGame예상안\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OzProject\UnityProject\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8078BC43-70D9-4454-986D-72EED7E734C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{405CB76A-D9FB-4D17-967B-07556DDD2760}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{22FD698F-1EA1-4536-86A9-BC1B31235C7D}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="31">
   <si>
     <t>고유ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -112,6 +112,33 @@
   <si>
     <t>Monster_02,Monster_05,Monster_06</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Monster_03,Monster_07</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BossMonster</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BossMonster_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BossMonster_02</t>
+  </si>
+  <si>
+    <t>BossMonster_03</t>
+  </si>
+  <si>
+    <t>BossMonster_04</t>
+  </si>
+  <si>
+    <t>BossMonster_05</t>
+  </si>
+  <si>
+    <t>BossMonster_06</t>
   </si>
 </sst>
 </file>
@@ -475,21 +502,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD1BB277-8C2D-4CB0-BB47-720EA44ED905}">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="20.5" customWidth="1"/>
-    <col min="2" max="2" width="33.796875" customWidth="1"/>
-    <col min="3" max="3" width="21.296875" customWidth="1"/>
-    <col min="4" max="4" width="20.796875" customWidth="1"/>
+    <col min="2" max="2" width="34.296875" customWidth="1"/>
+    <col min="3" max="3" width="25.796875" customWidth="1"/>
+    <col min="4" max="4" width="21.296875" customWidth="1"/>
+    <col min="5" max="5" width="20.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -499,8 +527,11 @@
       <c r="C2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -508,10 +539,13 @@
         <v>3</v>
       </c>
       <c r="C3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -519,10 +553,13 @@
         <v>14</v>
       </c>
       <c r="C4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -530,18 +567,27 @@
         <v>15</v>
       </c>
       <c r="C5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>9</v>
       </c>
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
       <c r="C6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -549,10 +595,13 @@
         <v>18</v>
       </c>
       <c r="C7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -560,10 +609,13 @@
         <v>20</v>
       </c>
       <c r="C8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -571,6 +623,9 @@
         <v>22</v>
       </c>
       <c r="C9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" t="s">
         <v>21</v>
       </c>
     </row>
